--- a/backend/cypress/fixtures/test_workbooks/corrective-action-plan-workbook.xlsx
+++ b/backend/cypress/fixtures/test_workbooks/corrective-action-plan-workbook.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lynnm\FAC\backend\schemas\output\excel\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82CB67E-8B3D-4E24-A7DB-6B93E8268699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661B6862-7C07-4953-B54E-96524C448A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="7590" yWindow="-12885" windowWidth="21345" windowHeight="11490" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="-15600" windowWidth="17280" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coversheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="section_name">Coversheet!$B$3</definedName>
     <definedName name="version">Coversheet!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -43,7 +43,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Section</t>
